--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="21000" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="95">
   <si>
     <t>游戏ID</t>
   </si>
@@ -597,6 +597,30 @@
   </si>
   <si>
     <t>105100101|105100102|105100103|105100104</t>
+  </si>
+  <si>
+    <t>黄金帝国</t>
+  </si>
+  <si>
+    <t>105400101|105400102|105400103|105400104</t>
+  </si>
+  <si>
+    <t>招财猫</t>
+  </si>
+  <si>
+    <t>100800101|100800102|100800103|100800104</t>
+  </si>
+  <si>
+    <t>麻将胡了2</t>
+  </si>
+  <si>
+    <t>赏金大对决</t>
+  </si>
+  <si>
+    <t>105700101|105700102|105700103|105700104</t>
+  </si>
+  <si>
+    <t>极速糖果1000</t>
   </si>
 </sst>
 </file>
@@ -813,6 +837,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
@@ -827,12 +857,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1327,7 +1351,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1392,6 +1416,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1734,7 +1761,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -3667,6 +3694,287 @@
         <v>1</v>
       </c>
     </row>
+    <row r="35" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A35" s="4">
+        <v>105400</v>
+      </c>
+      <c r="B35" s="4">
+        <v>105400001</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D35" s="4">
+        <v>0</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="4">
+        <v>1</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I35" s="4">
+        <v>5</v>
+      </c>
+      <c r="J35" s="4">
+        <v>6</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="21">
+        <v>1</v>
+      </c>
+      <c r="M35" s="21">
+        <v>1</v>
+      </c>
+      <c r="N35" s="4">
+        <v>20</v>
+      </c>
+      <c r="O35" s="4">
+        <v>1</v>
+      </c>
+      <c r="P35" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>1</v>
+      </c>
+      <c r="R35" s="13">
+        <v>1</v>
+      </c>
+      <c r="S35" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A36" s="4">
+        <v>100800</v>
+      </c>
+      <c r="B36" s="4">
+        <v>100800001</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D36" s="20">
+        <v>0</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="I36" s="4">
+        <v>6</v>
+      </c>
+      <c r="J36" s="4">
+        <v>6</v>
+      </c>
+      <c r="L36" s="21">
+        <v>1</v>
+      </c>
+      <c r="M36" s="21">
+        <v>1</v>
+      </c>
+      <c r="N36" s="4">
+        <v>20</v>
+      </c>
+      <c r="O36" s="4">
+        <v>1</v>
+      </c>
+      <c r="P36" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>1</v>
+      </c>
+      <c r="R36" s="13">
+        <v>1</v>
+      </c>
+      <c r="S36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A37" s="4">
+        <v>105300</v>
+      </c>
+      <c r="B37" s="4">
+        <v>105300001</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D37" s="20">
+        <v>0</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H37" s="4">
+        <v>0</v>
+      </c>
+      <c r="I37" s="4">
+        <v>5</v>
+      </c>
+      <c r="J37" s="4">
+        <v>5</v>
+      </c>
+      <c r="L37" s="21">
+        <v>1</v>
+      </c>
+      <c r="M37" s="21">
+        <v>1</v>
+      </c>
+      <c r="N37" s="4">
+        <v>20</v>
+      </c>
+      <c r="O37" s="4">
+        <v>1</v>
+      </c>
+      <c r="P37" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>1</v>
+      </c>
+      <c r="R37" s="13">
+        <v>1</v>
+      </c>
+      <c r="S37" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A38" s="4">
+        <v>105700</v>
+      </c>
+      <c r="B38" s="4">
+        <v>105700001</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D38" s="20">
+        <v>0</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="4">
+        <v>6</v>
+      </c>
+      <c r="J38" s="4">
+        <v>5</v>
+      </c>
+      <c r="L38" s="21">
+        <v>1</v>
+      </c>
+      <c r="M38" s="21">
+        <v>1</v>
+      </c>
+      <c r="N38" s="4">
+        <v>20</v>
+      </c>
+      <c r="O38" s="4">
+        <v>1</v>
+      </c>
+      <c r="P38" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>1</v>
+      </c>
+      <c r="R38" s="13">
+        <v>1</v>
+      </c>
+      <c r="S38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A39" s="4">
+        <v>105800</v>
+      </c>
+      <c r="B39" s="4">
+        <v>105800001</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="20">
+        <v>0</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H39" s="3">
+        <v>105800001</v>
+      </c>
+      <c r="I39" s="4">
+        <v>7</v>
+      </c>
+      <c r="J39" s="4">
+        <v>7</v>
+      </c>
+      <c r="L39" s="21">
+        <v>1</v>
+      </c>
+      <c r="M39" s="21">
+        <v>1</v>
+      </c>
+      <c r="N39" s="4">
+        <v>20</v>
+      </c>
+      <c r="O39" s="4">
+        <v>1</v>
+      </c>
+      <c r="P39" s="13">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>1</v>
+      </c>
+      <c r="R39" s="13">
+        <v>1</v>
+      </c>
+      <c r="S39" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="96">
   <si>
     <t>游戏ID</t>
   </si>
@@ -621,6 +621,9 @@
   </si>
   <si>
     <t>极速糖果1000</t>
+  </si>
+  <si>
+    <t>伽罗宝石</t>
   </si>
 </sst>
 </file>
@@ -837,8 +840,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -850,18 +858,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1761,7 +1764,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -3975,6 +3978,63 @@
         <v>1</v>
       </c>
     </row>
+    <row r="40" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A40" s="4">
+        <v>105500</v>
+      </c>
+      <c r="B40" s="4">
+        <v>105500001</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" s="20">
+        <v>1</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="4">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H40" s="3">
+        <v>105500101</v>
+      </c>
+      <c r="I40" s="4">
+        <v>3</v>
+      </c>
+      <c r="J40" s="4">
+        <v>4</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="21">
+        <v>1</v>
+      </c>
+      <c r="M40" s="21">
+        <v>1</v>
+      </c>
+      <c r="N40" s="4">
+        <v>5</v>
+      </c>
+      <c r="O40" s="4">
+        <v>1</v>
+      </c>
+      <c r="P40" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>1</v>
+      </c>
+      <c r="R40" s="4">
+        <v>1</v>
+      </c>
+      <c r="S40" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="99">
   <si>
     <t>游戏ID</t>
   </si>
@@ -624,6 +624,15 @@
   </si>
   <si>
     <t>伽罗宝石</t>
+  </si>
+  <si>
+    <t>超级高尔夫</t>
+  </si>
+  <si>
+    <t>104800101|104800102|104800103|104800104</t>
+  </si>
+  <si>
+    <t>伽罗宝石1</t>
   </si>
 </sst>
 </file>
@@ -840,8 +849,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -853,18 +874,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1764,7 +1773,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -4035,6 +4044,120 @@
         <v>1</v>
       </c>
     </row>
+    <row r="41" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A41" s="4">
+        <v>104800</v>
+      </c>
+      <c r="B41" s="4">
+        <v>104800001</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="20">
+        <v>0</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F41" s="4">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I41" s="4">
+        <v>6</v>
+      </c>
+      <c r="J41" s="4">
+        <v>6</v>
+      </c>
+      <c r="K41" s="4"/>
+      <c r="L41" s="21">
+        <v>1</v>
+      </c>
+      <c r="M41" s="21">
+        <v>1</v>
+      </c>
+      <c r="N41" s="4">
+        <v>20</v>
+      </c>
+      <c r="O41" s="4">
+        <v>1</v>
+      </c>
+      <c r="P41" s="4">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>1</v>
+      </c>
+      <c r="R41" s="4">
+        <v>1</v>
+      </c>
+      <c r="S41" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A42" s="4">
+        <v>105501</v>
+      </c>
+      <c r="B42" s="4">
+        <v>105501001</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D42" s="20">
+        <v>1</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42" s="4">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" s="3">
+        <v>105501101</v>
+      </c>
+      <c r="I42" s="4">
+        <v>3</v>
+      </c>
+      <c r="J42" s="4">
+        <v>4</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="21">
+        <v>1</v>
+      </c>
+      <c r="M42" s="21">
+        <v>1</v>
+      </c>
+      <c r="N42" s="4">
+        <v>5</v>
+      </c>
+      <c r="O42" s="4">
+        <v>1</v>
+      </c>
+      <c r="P42" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>1</v>
+      </c>
+      <c r="R42" s="4">
+        <v>1</v>
+      </c>
+      <c r="S42" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9EC3F69143C8EB40125425ADCFDD3C7CB9B2A431" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -27,13 +33,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -55,7 +61,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -79,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1">
+    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -104,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -139,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -161,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -183,7 +189,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1">
+    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
         <r>
           <rPr>
@@ -205,7 +211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
         <r>
           <rPr>
@@ -237,7 +243,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
         <r>
           <rPr>
@@ -270,7 +276,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="1">
+    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
         <r>
           <rPr>
@@ -293,7 +299,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="1">
+    <comment ref="R1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
         <r>
           <rPr>
@@ -318,7 +324,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="1">
+    <comment ref="S1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
         <r>
           <rPr>
@@ -638,14 +644,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="34">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -705,147 +705,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -884,8 +747,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -904,194 +773,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1114,256 +797,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1382,16 +823,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1406,16 +844,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1424,72 +859,25 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 2" xfId="49"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1767,605 +1155,604 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
     <col min="2" max="2" width="10.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="5" customWidth="1"/>
-    <col min="4" max="5" width="13.25" style="6" customWidth="1"/>
+    <col min="3" max="5" width="13.25" style="5" customWidth="1"/>
     <col min="6" max="7" width="9" style="5"/>
     <col min="8" max="8" width="51.125" style="5" customWidth="1"/>
     <col min="9" max="10" width="9" style="5"/>
     <col min="11" max="11" width="10.875" style="5" customWidth="1"/>
-    <col min="12" max="13" width="12.875" style="7" customWidth="1"/>
+    <col min="12" max="13" width="12.875" style="6" customWidth="1"/>
     <col min="14" max="18" width="9" style="5"/>
     <col min="19" max="19" width="14.125" style="5" customWidth="1"/>
     <col min="20" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21.95" customHeight="1" spans="1:19">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8" t="s">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="9"/>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="8"/>
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="7"/>
+      <c r="H1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="8" t="s">
+      <c r="I1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="8"/>
-      <c r="L1" s="10" t="s">
+      <c r="K1" s="7"/>
+      <c r="L1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:19" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="14" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="13" t="s">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13" t="s">
+      <c r="G2" s="12"/>
+      <c r="H2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="15" t="s">
+      <c r="K2" s="12"/>
+      <c r="L2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="16" t="s">
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
+      <c r="Q2" s="12"/>
+      <c r="R2" s="12"/>
+      <c r="S2" s="14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:19" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="17" t="s">
+      <c r="C3" s="11"/>
+      <c r="D3" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="17"/>
-      <c r="F3" s="13" t="s">
+      <c r="E3" s="15"/>
+      <c r="F3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13" t="s">
+      <c r="G3" s="12"/>
+      <c r="H3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="13"/>
-      <c r="L3" s="15" t="s">
+      <c r="K3" s="12"/>
+      <c r="L3" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="16" t="s">
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="16"/>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A5" s="12">
+    <row r="4" spans="1:19" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="14"/>
+    </row>
+    <row r="5" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
         <v>100100</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="11">
         <v>100100026</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="17">
-        <v>1</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="D5" s="15">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="13">
-        <v>0</v>
-      </c>
-      <c r="G5" s="13" t="s">
+      <c r="F5" s="12">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <v>4</v>
       </c>
-      <c r="J5" s="13">
-        <v>5</v>
-      </c>
-      <c r="K5" s="18" t="s">
+      <c r="J5" s="12">
+        <v>5</v>
+      </c>
+      <c r="K5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="L5" s="15">
-        <v>1</v>
-      </c>
-      <c r="M5" s="15">
+      <c r="L5" s="13">
+        <v>1</v>
+      </c>
+      <c r="M5" s="13">
         <v>2</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <v>50</v>
       </c>
-      <c r="O5" s="13">
-        <v>1</v>
-      </c>
-      <c r="P5" s="13">
+      <c r="O5" s="12">
+        <v>1</v>
+      </c>
+      <c r="P5" s="12">
         <f>N5*M5*L5*O5</f>
         <v>100</v>
       </c>
-      <c r="Q5" s="13">
-        <v>5</v>
-      </c>
-      <c r="R5" s="13">
+      <c r="Q5" s="12">
+        <v>5</v>
+      </c>
+      <c r="R5" s="12">
         <f>P5*Q5/N5/M5</f>
         <v>5</v>
       </c>
-      <c r="S5" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A6" s="12">
+      <c r="S5" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
         <v>100300</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="11">
         <v>100300001</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="17">
-        <v>1</v>
-      </c>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="15">
+        <v>1</v>
+      </c>
+      <c r="E6" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="13">
-        <v>0</v>
-      </c>
-      <c r="G6" s="13" t="s">
+      <c r="F6" s="12">
+        <v>0</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <v>3</v>
       </c>
-      <c r="J6" s="13">
+      <c r="J6" s="12">
         <v>3</v>
       </c>
-      <c r="K6" s="13"/>
-      <c r="L6" s="15">
-        <v>1</v>
-      </c>
-      <c r="M6" s="15">
-        <v>1</v>
-      </c>
-      <c r="N6" s="13">
-        <v>1</v>
-      </c>
-      <c r="O6" s="13">
-        <v>1</v>
-      </c>
-      <c r="P6" s="13">
+      <c r="K6" s="12"/>
+      <c r="L6" s="13">
+        <v>1</v>
+      </c>
+      <c r="M6" s="13">
+        <v>1</v>
+      </c>
+      <c r="N6" s="12">
+        <v>1</v>
+      </c>
+      <c r="O6" s="12">
+        <v>1</v>
+      </c>
+      <c r="P6" s="12">
         <f t="shared" ref="P6:P32" si="0">N6*M6*L6*O6</f>
         <v>1</v>
       </c>
-      <c r="Q6" s="13">
-        <v>1</v>
-      </c>
-      <c r="R6" s="13">
+      <c r="Q6" s="12">
+        <v>1</v>
+      </c>
+      <c r="R6" s="12">
         <f t="shared" ref="R6:R32" si="1">P6*Q6/N6/M6</f>
         <v>1</v>
       </c>
-      <c r="S6" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A7" s="12">
+      <c r="S6" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
         <v>100700</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="11">
         <v>100700001</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="17">
-        <v>0</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="15">
+        <v>0</v>
+      </c>
+      <c r="E7" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="13">
-        <v>1</v>
-      </c>
-      <c r="G7" s="13" t="s">
+      <c r="F7" s="12">
+        <v>1</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="13">
-        <v>0</v>
-      </c>
-      <c r="I7" s="13">
+      <c r="H7" s="12">
+        <v>0</v>
+      </c>
+      <c r="I7" s="12">
         <v>4</v>
       </c>
-      <c r="J7" s="13">
-        <v>5</v>
-      </c>
-      <c r="K7" s="13"/>
-      <c r="L7" s="15">
-        <v>1</v>
-      </c>
-      <c r="M7" s="15">
-        <v>1</v>
-      </c>
-      <c r="N7" s="13">
+      <c r="J7" s="12">
+        <v>5</v>
+      </c>
+      <c r="K7" s="12"/>
+      <c r="L7" s="13">
+        <v>1</v>
+      </c>
+      <c r="M7" s="13">
+        <v>1</v>
+      </c>
+      <c r="N7" s="12">
         <v>20</v>
       </c>
-      <c r="O7" s="13">
+      <c r="O7" s="12">
         <v>0.05</v>
       </c>
-      <c r="P7" s="13">
+      <c r="P7" s="12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q7" s="13">
+      <c r="Q7" s="12">
         <v>2</v>
       </c>
-      <c r="R7" s="13">
+      <c r="R7" s="12">
         <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="S7" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A8" s="12">
+      <c r="S7" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
         <v>101200</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="11">
         <v>101200001</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="17">
-        <v>1</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="15">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="s">
+      <c r="F8" s="12">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="13">
-        <v>0</v>
-      </c>
-      <c r="I8" s="13">
+      <c r="H8" s="12">
+        <v>0</v>
+      </c>
+      <c r="I8" s="12">
         <v>3</v>
       </c>
-      <c r="J8" s="13">
-        <v>5</v>
-      </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="15">
-        <v>1</v>
-      </c>
-      <c r="M8" s="15">
-        <v>1</v>
-      </c>
-      <c r="N8" s="13">
+      <c r="J8" s="12">
+        <v>5</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="13">
+        <v>1</v>
+      </c>
+      <c r="M8" s="13">
+        <v>1</v>
+      </c>
+      <c r="N8" s="12">
         <v>15</v>
       </c>
-      <c r="O8" s="13">
-        <v>1</v>
-      </c>
-      <c r="P8" s="13">
+      <c r="O8" s="12">
+        <v>1</v>
+      </c>
+      <c r="P8" s="12">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q8" s="13">
-        <v>1</v>
-      </c>
-      <c r="R8" s="13">
+      <c r="Q8" s="12">
+        <v>1</v>
+      </c>
+      <c r="R8" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S8" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A9" s="12">
+      <c r="S8" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="11">
         <v>101400</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <v>101400001</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="17">
-        <v>0</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="D9" s="15">
+        <v>0</v>
+      </c>
+      <c r="E9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="13">
-        <v>0</v>
-      </c>
-      <c r="G9" s="13" t="s">
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <v>101400101</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <v>4</v>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <v>3</v>
       </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="15">
-        <v>1</v>
-      </c>
-      <c r="M9" s="15">
-        <v>1</v>
-      </c>
-      <c r="N9" s="13">
+      <c r="K9" s="12"/>
+      <c r="L9" s="13">
+        <v>1</v>
+      </c>
+      <c r="M9" s="13">
+        <v>1</v>
+      </c>
+      <c r="N9" s="12">
         <v>10</v>
       </c>
-      <c r="O9" s="13">
+      <c r="O9" s="12">
         <v>0.05</v>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="12">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="Q9" s="13">
+      <c r="Q9" s="12">
         <v>6</v>
       </c>
-      <c r="R9" s="13">
+      <c r="R9" s="12">
         <f t="shared" si="1"/>
         <v>0.3</v>
       </c>
-      <c r="S9" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A10" s="12">
+      <c r="S9" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="11">
         <v>102400</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <v>102400026</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="17">
-        <v>1</v>
-      </c>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="15">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="13">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13" t="s">
+      <c r="F10" s="12">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <v>4</v>
       </c>
-      <c r="J10" s="13">
-        <v>5</v>
-      </c>
-      <c r="K10" s="18" t="s">
+      <c r="J10" s="12">
+        <v>5</v>
+      </c>
+      <c r="K10" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="15">
-        <v>1</v>
-      </c>
-      <c r="M10" s="15">
+      <c r="L10" s="13">
+        <v>1</v>
+      </c>
+      <c r="M10" s="13">
         <v>2</v>
       </c>
-      <c r="N10" s="13">
+      <c r="N10" s="12">
         <v>50</v>
       </c>
-      <c r="O10" s="13">
-        <v>1</v>
-      </c>
-      <c r="P10" s="13">
+      <c r="O10" s="12">
+        <v>1</v>
+      </c>
+      <c r="P10" s="12">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="Q10" s="13">
-        <v>5</v>
-      </c>
-      <c r="R10" s="13">
+      <c r="Q10" s="12">
+        <v>5</v>
+      </c>
+      <c r="R10" s="12">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="S10" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A11" s="12">
+      <c r="S10" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="11">
         <v>101700</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <v>101700001</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="17">
-        <v>0</v>
-      </c>
-      <c r="E11" s="17" t="s">
+      <c r="D11" s="15">
+        <v>0</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="13">
-        <v>1</v>
-      </c>
-      <c r="G11" s="13" t="s">
+      <c r="F11" s="12">
+        <v>1</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <v>4</v>
       </c>
-      <c r="J11" s="13">
-        <v>5</v>
-      </c>
-      <c r="K11" s="13"/>
-      <c r="L11" s="15">
-        <v>1</v>
-      </c>
-      <c r="M11" s="15">
-        <v>1</v>
-      </c>
-      <c r="N11" s="13">
+      <c r="J11" s="12">
+        <v>5</v>
+      </c>
+      <c r="K11" s="12"/>
+      <c r="L11" s="13">
+        <v>1</v>
+      </c>
+      <c r="M11" s="13">
+        <v>1</v>
+      </c>
+      <c r="N11" s="12">
         <v>20</v>
       </c>
-      <c r="O11" s="13">
-        <v>1</v>
-      </c>
-      <c r="P11" s="13">
+      <c r="O11" s="12">
+        <v>1</v>
+      </c>
+      <c r="P11" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="Q11" s="13">
+      <c r="Q11" s="12">
         <v>2</v>
       </c>
-      <c r="R11" s="13">
+      <c r="R11" s="12">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="S11" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S11" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>102200</v>
       </c>
@@ -2375,19 +1762,19 @@
       <c r="C12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="17">
-        <v>1</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="D12" s="15">
+        <v>1</v>
+      </c>
+      <c r="E12" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="13">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13" t="s">
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="12" t="s">
         <v>46</v>
       </c>
       <c r="I12" s="3">
@@ -2396,34 +1783,34 @@
       <c r="J12" s="3">
         <v>5</v>
       </c>
-      <c r="L12" s="19">
-        <v>1</v>
-      </c>
-      <c r="M12" s="19">
+      <c r="L12" s="17">
+        <v>1</v>
+      </c>
+      <c r="M12" s="17">
         <v>1</v>
       </c>
       <c r="N12" s="3">
         <v>25</v>
       </c>
-      <c r="O12" s="13">
-        <v>1</v>
-      </c>
-      <c r="P12" s="13">
+      <c r="O12" s="12">
+        <v>1</v>
+      </c>
+      <c r="P12" s="12">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="Q12" s="13">
-        <v>1</v>
-      </c>
-      <c r="R12" s="13">
+      <c r="Q12" s="12">
+        <v>1</v>
+      </c>
+      <c r="R12" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S12" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S12" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>102100</v>
       </c>
@@ -2433,19 +1820,19 @@
       <c r="C13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="17">
-        <v>0</v>
-      </c>
-      <c r="E13" s="17" t="s">
+      <c r="D13" s="15">
+        <v>0</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="13">
-        <v>1</v>
-      </c>
-      <c r="G13" s="13" t="s">
+      <c r="F13" s="12">
+        <v>1</v>
+      </c>
+      <c r="G13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="12" t="s">
         <v>48</v>
       </c>
       <c r="I13" s="3">
@@ -2454,34 +1841,34 @@
       <c r="J13" s="3">
         <v>5</v>
       </c>
-      <c r="L13" s="19">
-        <v>1</v>
-      </c>
-      <c r="M13" s="19">
+      <c r="L13" s="17">
+        <v>1</v>
+      </c>
+      <c r="M13" s="17">
         <v>1</v>
       </c>
       <c r="N13" s="3">
         <v>20</v>
       </c>
-      <c r="O13" s="13">
-        <v>1</v>
-      </c>
-      <c r="P13" s="13">
+      <c r="O13" s="12">
+        <v>1</v>
+      </c>
+      <c r="P13" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="Q13" s="13">
-        <v>1</v>
-      </c>
-      <c r="R13" s="13">
+      <c r="Q13" s="12">
+        <v>1</v>
+      </c>
+      <c r="R13" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S13" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S13" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>101800</v>
       </c>
@@ -2491,19 +1878,19 @@
       <c r="C14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="17">
-        <v>0</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="D14" s="15">
+        <v>0</v>
+      </c>
+      <c r="E14" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13" t="s">
+      <c r="F14" s="12">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H14" s="13" t="s">
+      <c r="H14" s="12" t="s">
         <v>50</v>
       </c>
       <c r="I14" s="3">
@@ -2512,34 +1899,34 @@
       <c r="J14" s="3">
         <v>6</v>
       </c>
-      <c r="L14" s="19">
-        <v>1</v>
-      </c>
-      <c r="M14" s="19">
+      <c r="L14" s="17">
+        <v>1</v>
+      </c>
+      <c r="M14" s="17">
         <v>1</v>
       </c>
       <c r="N14" s="3">
         <v>20</v>
       </c>
-      <c r="O14" s="13">
-        <v>1</v>
-      </c>
-      <c r="P14" s="13">
+      <c r="O14" s="12">
+        <v>1</v>
+      </c>
+      <c r="P14" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="Q14" s="13">
-        <v>1</v>
-      </c>
-      <c r="R14" s="13">
+      <c r="Q14" s="12">
+        <v>1</v>
+      </c>
+      <c r="R14" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S14" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S14" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>102500</v>
       </c>
@@ -2549,19 +1936,19 @@
       <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="17">
-        <v>1</v>
-      </c>
-      <c r="E15" s="17" t="s">
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="13">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13" t="s">
+      <c r="F15" s="12">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="13" t="s">
+      <c r="H15" s="12" t="s">
         <v>52</v>
       </c>
       <c r="I15" s="3">
@@ -2570,34 +1957,34 @@
       <c r="J15" s="3">
         <v>5</v>
       </c>
-      <c r="L15" s="19">
-        <v>1</v>
-      </c>
-      <c r="M15" s="19">
+      <c r="L15" s="17">
+        <v>1</v>
+      </c>
+      <c r="M15" s="17">
         <v>1</v>
       </c>
       <c r="N15" s="3">
         <v>50</v>
       </c>
-      <c r="O15" s="13">
-        <v>1</v>
-      </c>
-      <c r="P15" s="13">
+      <c r="O15" s="12">
+        <v>1</v>
+      </c>
+      <c r="P15" s="12">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="Q15" s="13">
-        <v>1</v>
-      </c>
-      <c r="R15" s="13">
+      <c r="Q15" s="12">
+        <v>1</v>
+      </c>
+      <c r="R15" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S15" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S15" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>102300</v>
       </c>
@@ -2607,19 +1994,19 @@
       <c r="C16" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="17">
-        <v>0</v>
-      </c>
-      <c r="E16" s="17" t="s">
+      <c r="D16" s="15">
+        <v>0</v>
+      </c>
+      <c r="E16" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="13">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13" t="s">
+      <c r="F16" s="12">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="13" t="s">
+      <c r="H16" s="12" t="s">
         <v>54</v>
       </c>
       <c r="I16" s="3">
@@ -2628,34 +2015,34 @@
       <c r="J16" s="3">
         <v>5</v>
       </c>
-      <c r="L16" s="19">
-        <v>1</v>
-      </c>
-      <c r="M16" s="19">
+      <c r="L16" s="17">
+        <v>1</v>
+      </c>
+      <c r="M16" s="17">
         <v>1</v>
       </c>
       <c r="N16" s="3">
         <v>20</v>
       </c>
-      <c r="O16" s="13">
-        <v>1</v>
-      </c>
-      <c r="P16" s="13">
+      <c r="O16" s="12">
+        <v>1</v>
+      </c>
+      <c r="P16" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="Q16" s="13">
-        <v>1</v>
-      </c>
-      <c r="R16" s="13">
+      <c r="Q16" s="12">
+        <v>1</v>
+      </c>
+      <c r="R16" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S16" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S16" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>103400</v>
       </c>
@@ -2665,19 +2052,19 @@
       <c r="C17" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D17" s="17">
-        <v>1</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="D17" s="15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="13">
-        <v>0</v>
-      </c>
-      <c r="G17" s="13" t="s">
+      <c r="F17" s="12">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="12">
         <v>103400101</v>
       </c>
       <c r="I17" s="3">
@@ -2686,34 +2073,34 @@
       <c r="J17" s="3">
         <v>3</v>
       </c>
-      <c r="L17" s="19">
-        <v>1</v>
-      </c>
-      <c r="M17" s="19">
+      <c r="L17" s="17">
+        <v>1</v>
+      </c>
+      <c r="M17" s="17">
         <v>1</v>
       </c>
       <c r="N17" s="3">
         <v>5</v>
       </c>
-      <c r="O17" s="13">
-        <v>1</v>
-      </c>
-      <c r="P17" s="13">
+      <c r="O17" s="12">
+        <v>1</v>
+      </c>
+      <c r="P17" s="12">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q17" s="13">
-        <v>1</v>
-      </c>
-      <c r="R17" s="13">
+      <c r="Q17" s="12">
+        <v>1</v>
+      </c>
+      <c r="R17" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S17" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S17" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>103500</v>
       </c>
@@ -2723,19 +2110,19 @@
       <c r="C18" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="17">
-        <v>1</v>
-      </c>
-      <c r="E18" s="17" t="s">
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="13">
-        <v>0</v>
-      </c>
-      <c r="G18" s="13" t="s">
+      <c r="F18" s="12">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H18" s="13" t="s">
+      <c r="H18" s="12" t="s">
         <v>57</v>
       </c>
       <c r="I18" s="3">
@@ -2744,34 +2131,34 @@
       <c r="J18" s="3">
         <v>3</v>
       </c>
-      <c r="L18" s="19">
-        <v>1</v>
-      </c>
-      <c r="M18" s="19">
+      <c r="L18" s="17">
+        <v>1</v>
+      </c>
+      <c r="M18" s="17">
         <v>1</v>
       </c>
       <c r="N18" s="3">
         <v>10</v>
       </c>
-      <c r="O18" s="13">
-        <v>1</v>
-      </c>
-      <c r="P18" s="13">
+      <c r="O18" s="12">
+        <v>1</v>
+      </c>
+      <c r="P18" s="12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="Q18" s="13">
-        <v>1</v>
-      </c>
-      <c r="R18" s="13">
+      <c r="Q18" s="12">
+        <v>1</v>
+      </c>
+      <c r="R18" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S18" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S18" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>103501</v>
       </c>
@@ -2781,19 +2168,19 @@
       <c r="C19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="17">
-        <v>1</v>
-      </c>
-      <c r="E19" s="17" t="s">
+      <c r="D19" s="15">
+        <v>1</v>
+      </c>
+      <c r="E19" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F19" s="13">
-        <v>0</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="F19" s="12">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H19" s="13" t="s">
+      <c r="H19" s="12" t="s">
         <v>59</v>
       </c>
       <c r="I19" s="3">
@@ -2802,34 +2189,34 @@
       <c r="J19" s="3">
         <v>3</v>
       </c>
-      <c r="L19" s="19">
-        <v>1</v>
-      </c>
-      <c r="M19" s="19">
+      <c r="L19" s="17">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17">
         <v>1</v>
       </c>
       <c r="N19" s="3">
         <v>10</v>
       </c>
-      <c r="O19" s="13">
-        <v>1</v>
-      </c>
-      <c r="P19" s="13">
+      <c r="O19" s="12">
+        <v>1</v>
+      </c>
+      <c r="P19" s="12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="Q19" s="13">
-        <v>1</v>
-      </c>
-      <c r="R19" s="13">
+      <c r="Q19" s="12">
+        <v>1</v>
+      </c>
+      <c r="R19" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S19" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S19" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>103600</v>
       </c>
@@ -2839,19 +2226,19 @@
       <c r="C20" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="17">
-        <v>1</v>
-      </c>
-      <c r="E20" s="17" t="s">
+      <c r="D20" s="15">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="13">
-        <v>0</v>
-      </c>
-      <c r="G20" s="13" t="s">
+      <c r="F20" s="12">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="12">
         <v>103600101</v>
       </c>
       <c r="I20" s="3">
@@ -2860,34 +2247,34 @@
       <c r="J20" s="3">
         <v>3</v>
       </c>
-      <c r="L20" s="19">
-        <v>1</v>
-      </c>
-      <c r="M20" s="19">
+      <c r="L20" s="17">
+        <v>1</v>
+      </c>
+      <c r="M20" s="17">
         <v>1</v>
       </c>
       <c r="N20" s="3">
         <v>5</v>
       </c>
-      <c r="O20" s="13">
-        <v>1</v>
-      </c>
-      <c r="P20" s="13">
+      <c r="O20" s="12">
+        <v>1</v>
+      </c>
+      <c r="P20" s="12">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q20" s="13">
-        <v>1</v>
-      </c>
-      <c r="R20" s="13">
+      <c r="Q20" s="12">
+        <v>1</v>
+      </c>
+      <c r="R20" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S20" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S20" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>102800</v>
       </c>
@@ -2897,19 +2284,19 @@
       <c r="C21" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D21" s="17">
-        <v>0</v>
-      </c>
-      <c r="E21" s="17" t="s">
+      <c r="D21" s="15">
+        <v>0</v>
+      </c>
+      <c r="E21" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F21" s="13">
-        <v>1</v>
-      </c>
-      <c r="G21" s="13" t="s">
+      <c r="F21" s="12">
+        <v>1</v>
+      </c>
+      <c r="G21" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="12" t="s">
         <v>62</v>
       </c>
       <c r="I21" s="3">
@@ -2918,34 +2305,34 @@
       <c r="J21" s="3">
         <v>6</v>
       </c>
-      <c r="L21" s="19">
-        <v>1</v>
-      </c>
-      <c r="M21" s="19">
+      <c r="L21" s="17">
+        <v>1</v>
+      </c>
+      <c r="M21" s="17">
         <v>1</v>
       </c>
       <c r="N21" s="3">
         <v>20</v>
       </c>
-      <c r="O21" s="13">
-        <v>1</v>
-      </c>
-      <c r="P21" s="13">
+      <c r="O21" s="12">
+        <v>1</v>
+      </c>
+      <c r="P21" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="Q21" s="13">
-        <v>1</v>
-      </c>
-      <c r="R21" s="13">
+      <c r="Q21" s="12">
+        <v>1</v>
+      </c>
+      <c r="R21" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S21" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S21" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>103401</v>
       </c>
@@ -2955,19 +2342,19 @@
       <c r="C22" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D22" s="17">
-        <v>1</v>
-      </c>
-      <c r="E22" s="17" t="s">
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="13">
-        <v>0</v>
-      </c>
-      <c r="G22" s="13" t="s">
+      <c r="F22" s="12">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="12">
         <v>103401101</v>
       </c>
       <c r="I22" s="3">
@@ -2976,34 +2363,34 @@
       <c r="J22" s="3">
         <v>3</v>
       </c>
-      <c r="L22" s="19">
-        <v>1</v>
-      </c>
-      <c r="M22" s="19">
+      <c r="L22" s="17">
+        <v>1</v>
+      </c>
+      <c r="M22" s="17">
         <v>1</v>
       </c>
       <c r="N22" s="3">
         <v>5</v>
       </c>
-      <c r="O22" s="13">
-        <v>1</v>
-      </c>
-      <c r="P22" s="13">
+      <c r="O22" s="12">
+        <v>1</v>
+      </c>
+      <c r="P22" s="12">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="Q22" s="13">
-        <v>1</v>
-      </c>
-      <c r="R22" s="13">
+      <c r="Q22" s="12">
+        <v>1</v>
+      </c>
+      <c r="R22" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S22" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S22" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>102000</v>
       </c>
@@ -3013,19 +2400,19 @@
       <c r="C23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="17">
-        <v>1</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="F23" s="13">
-        <v>0</v>
-      </c>
-      <c r="G23" s="13" t="s">
+      <c r="F23" s="12">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="13" t="s">
+      <c r="H23" s="12" t="s">
         <v>65</v>
       </c>
       <c r="I23" s="3">
@@ -3034,34 +2421,34 @@
       <c r="J23" s="3">
         <v>5</v>
       </c>
-      <c r="L23" s="19">
-        <v>1</v>
-      </c>
-      <c r="M23" s="19">
+      <c r="L23" s="17">
+        <v>1</v>
+      </c>
+      <c r="M23" s="17">
         <v>1</v>
       </c>
       <c r="N23" s="3">
         <v>15</v>
       </c>
-      <c r="O23" s="13">
-        <v>1</v>
-      </c>
-      <c r="P23" s="13">
+      <c r="O23" s="12">
+        <v>1</v>
+      </c>
+      <c r="P23" s="12">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="Q23" s="13">
-        <v>1</v>
-      </c>
-      <c r="R23" s="13">
+      <c r="Q23" s="12">
+        <v>1</v>
+      </c>
+      <c r="R23" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="S23" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" s="4" customFormat="1" ht="16.5" spans="1:19">
+      <c r="S23" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>103800</v>
       </c>
@@ -3071,19 +2458,19 @@
       <c r="C24" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="20">
-        <v>1</v>
-      </c>
-      <c r="E24" s="17" t="s">
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="15" t="s">
         <v>30</v>
       </c>
       <c r="F24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H24" s="12" t="s">
         <v>67</v>
       </c>
       <c r="I24" s="4">
@@ -3092,11 +2479,10 @@
       <c r="J24" s="4">
         <v>5</v>
       </c>
-      <c r="K24" s="4"/>
-      <c r="L24" s="21">
-        <v>1</v>
-      </c>
-      <c r="M24" s="21">
+      <c r="L24" s="18">
+        <v>1</v>
+      </c>
+      <c r="M24" s="18">
         <v>1</v>
       </c>
       <c r="N24" s="4">
@@ -3105,14 +2491,14 @@
       <c r="O24" s="4">
         <v>1</v>
       </c>
-      <c r="P24" s="13">
+      <c r="P24" s="12">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="Q24" s="4">
         <v>1</v>
       </c>
-      <c r="R24" s="13">
+      <c r="R24" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3120,7 +2506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="25" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>102700</v>
       </c>
@@ -3130,19 +2516,19 @@
       <c r="C25" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="20">
-        <v>0</v>
-      </c>
-      <c r="E25" s="17" t="s">
+      <c r="D25" s="4">
+        <v>0</v>
+      </c>
+      <c r="E25" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="12" t="s">
         <v>69</v>
       </c>
       <c r="I25" s="4">
@@ -3151,11 +2537,10 @@
       <c r="J25" s="4">
         <v>5</v>
       </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="21">
-        <v>1</v>
-      </c>
-      <c r="M25" s="21">
+      <c r="L25" s="18">
+        <v>1</v>
+      </c>
+      <c r="M25" s="18">
         <v>1</v>
       </c>
       <c r="N25" s="4">
@@ -3164,14 +2549,14 @@
       <c r="O25" s="4">
         <v>1</v>
       </c>
-      <c r="P25" s="13">
+      <c r="P25" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="Q25" s="4">
         <v>1</v>
       </c>
-      <c r="R25" s="13">
+      <c r="R25" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3179,7 +2564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="26" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>103700</v>
       </c>
@@ -3189,19 +2574,19 @@
       <c r="C26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="20">
-        <v>1</v>
-      </c>
-      <c r="E26" s="17" t="s">
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="15" t="s">
         <v>30</v>
       </c>
       <c r="F26" s="4">
         <v>0</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="12">
         <v>103700101</v>
       </c>
       <c r="I26" s="4">
@@ -3210,11 +2595,10 @@
       <c r="J26" s="4">
         <v>3</v>
       </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="21">
-        <v>1</v>
-      </c>
-      <c r="M26" s="21">
+      <c r="L26" s="18">
+        <v>1</v>
+      </c>
+      <c r="M26" s="18">
         <v>1</v>
       </c>
       <c r="N26" s="4">
@@ -3223,14 +2607,14 @@
       <c r="O26" s="4">
         <v>1</v>
       </c>
-      <c r="P26" s="13">
+      <c r="P26" s="12">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="Q26" s="4">
         <v>1</v>
       </c>
-      <c r="R26" s="13">
+      <c r="R26" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3238,7 +2622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="27" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>103100</v>
       </c>
@@ -3248,19 +2632,19 @@
       <c r="C27" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D27" s="20">
-        <v>1</v>
-      </c>
-      <c r="E27" s="17" t="s">
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15" t="s">
         <v>30</v>
       </c>
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H27" s="13" t="s">
+      <c r="H27" s="12" t="s">
         <v>72</v>
       </c>
       <c r="I27" s="4">
@@ -3269,11 +2653,10 @@
       <c r="J27" s="4">
         <v>5</v>
       </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="21">
-        <v>1</v>
-      </c>
-      <c r="M27" s="21">
+      <c r="L27" s="18">
+        <v>1</v>
+      </c>
+      <c r="M27" s="18">
         <v>1</v>
       </c>
       <c r="N27" s="4">
@@ -3282,14 +2665,14 @@
       <c r="O27" s="4">
         <v>1</v>
       </c>
-      <c r="P27" s="13">
+      <c r="P27" s="12">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="Q27" s="4">
         <v>1</v>
       </c>
-      <c r="R27" s="13">
+      <c r="R27" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3297,7 +2680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="28" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>104000</v>
       </c>
@@ -3307,19 +2690,19 @@
       <c r="C28" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="20">
-        <v>1</v>
-      </c>
-      <c r="E28" s="17" t="s">
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>30</v>
       </c>
       <c r="F28" s="4">
         <v>0</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="12" t="s">
         <v>74</v>
       </c>
       <c r="I28" s="4">
@@ -3328,11 +2711,10 @@
       <c r="J28" s="4">
         <v>5</v>
       </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="21">
-        <v>1</v>
-      </c>
-      <c r="M28" s="21">
+      <c r="L28" s="18">
+        <v>1</v>
+      </c>
+      <c r="M28" s="18">
         <v>1</v>
       </c>
       <c r="N28" s="4">
@@ -3341,14 +2723,14 @@
       <c r="O28" s="4">
         <v>1</v>
       </c>
-      <c r="P28" s="13">
+      <c r="P28" s="12">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="Q28" s="4">
         <v>1</v>
       </c>
-      <c r="R28" s="13">
+      <c r="R28" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3356,7 +2738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="29" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>103900</v>
       </c>
@@ -3366,19 +2748,19 @@
       <c r="C29" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="20">
-        <v>1</v>
-      </c>
-      <c r="E29" s="17" t="s">
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>30</v>
       </c>
       <c r="F29" s="4">
         <v>0</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H29" s="12" t="s">
         <v>76</v>
       </c>
       <c r="I29" s="4">
@@ -3387,11 +2769,10 @@
       <c r="J29" s="4">
         <v>5</v>
       </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="21">
-        <v>1</v>
-      </c>
-      <c r="M29" s="21">
+      <c r="L29" s="18">
+        <v>1</v>
+      </c>
+      <c r="M29" s="18">
         <v>1</v>
       </c>
       <c r="N29" s="4">
@@ -3400,14 +2781,14 @@
       <c r="O29" s="4">
         <v>1</v>
       </c>
-      <c r="P29" s="13">
+      <c r="P29" s="12">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="Q29" s="4">
         <v>1</v>
       </c>
-      <c r="R29" s="13">
+      <c r="R29" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3415,7 +2796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="30" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>101600</v>
       </c>
@@ -3425,19 +2806,19 @@
       <c r="C30" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="20">
-        <v>0</v>
-      </c>
-      <c r="E30" s="17" t="s">
+      <c r="D30" s="4">
+        <v>0</v>
+      </c>
+      <c r="E30" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F30" s="4">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="12" t="s">
         <v>78</v>
       </c>
       <c r="I30" s="4">
@@ -3446,11 +2827,10 @@
       <c r="J30" s="4">
         <v>6</v>
       </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="21">
-        <v>1</v>
-      </c>
-      <c r="M30" s="21">
+      <c r="L30" s="18">
+        <v>1</v>
+      </c>
+      <c r="M30" s="18">
         <v>1</v>
       </c>
       <c r="N30" s="4">
@@ -3459,14 +2839,14 @@
       <c r="O30" s="4">
         <v>1</v>
       </c>
-      <c r="P30" s="13">
+      <c r="P30" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="Q30" s="4">
         <v>1</v>
       </c>
-      <c r="R30" s="13">
+      <c r="R30" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3474,7 +2854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="31" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>101500</v>
       </c>
@@ -3484,19 +2864,19 @@
       <c r="C31" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="20">
-        <v>0</v>
-      </c>
-      <c r="E31" s="17" t="s">
+      <c r="D31" s="4">
+        <v>0</v>
+      </c>
+      <c r="E31" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F31" s="4">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="12" t="s">
         <v>80</v>
       </c>
       <c r="I31" s="4">
@@ -3505,11 +2885,10 @@
       <c r="J31" s="4">
         <v>5</v>
       </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="21">
-        <v>1</v>
-      </c>
-      <c r="M31" s="21">
+      <c r="L31" s="18">
+        <v>1</v>
+      </c>
+      <c r="M31" s="18">
         <v>1</v>
       </c>
       <c r="N31" s="4">
@@ -3518,14 +2897,14 @@
       <c r="O31" s="4">
         <v>1</v>
       </c>
-      <c r="P31" s="13">
+      <c r="P31" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="Q31" s="4">
         <v>1</v>
       </c>
-      <c r="R31" s="13">
+      <c r="R31" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3533,7 +2912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="32" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>102600</v>
       </c>
@@ -3543,16 +2922,16 @@
       <c r="C32" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D32" s="20">
-        <v>0</v>
-      </c>
-      <c r="E32" s="17" t="s">
+      <c r="D32" s="4">
+        <v>0</v>
+      </c>
+      <c r="E32" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F32" s="4">
         <v>1</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="12" t="s">
         <v>38</v>
       </c>
       <c r="H32" s="3" t="s">
@@ -3564,11 +2943,10 @@
       <c r="J32" s="4">
         <v>6</v>
       </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="21">
-        <v>1</v>
-      </c>
-      <c r="M32" s="21">
+      <c r="L32" s="18">
+        <v>1</v>
+      </c>
+      <c r="M32" s="18">
         <v>1</v>
       </c>
       <c r="N32" s="4">
@@ -3577,14 +2955,14 @@
       <c r="O32" s="4">
         <v>1</v>
       </c>
-      <c r="P32" s="13">
+      <c r="P32" s="12">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="Q32" s="4">
         <v>1</v>
       </c>
-      <c r="R32" s="13">
+      <c r="R32" s="12">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
@@ -3592,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="16.5" spans="1:19">
+    <row r="33" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>105000</v>
       </c>
@@ -3605,13 +2983,13 @@
       <c r="D33" s="4">
         <v>0</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F33" s="4">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="12" t="s">
         <v>38</v>
       </c>
       <c r="H33" s="3" t="s">
@@ -3624,10 +3002,10 @@
         <v>6</v>
       </c>
       <c r="K33" s="4"/>
-      <c r="L33" s="21">
-        <v>1</v>
-      </c>
-      <c r="M33" s="21">
+      <c r="L33" s="18">
+        <v>1</v>
+      </c>
+      <c r="M33" s="18">
         <v>1</v>
       </c>
       <c r="N33" s="4">
@@ -3636,20 +3014,20 @@
       <c r="O33" s="4">
         <v>1</v>
       </c>
-      <c r="P33" s="13">
+      <c r="P33" s="12">
         <v>20</v>
       </c>
       <c r="Q33" s="4">
         <v>1</v>
       </c>
-      <c r="R33" s="13">
+      <c r="R33" s="12">
         <v>1</v>
       </c>
       <c r="S33" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="34" customFormat="1" ht="16.5" spans="1:19">
+    <row r="34" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>105100</v>
       </c>
@@ -3659,10 +3037,10 @@
       <c r="C34" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D34" s="6">
-        <v>0</v>
-      </c>
-      <c r="E34" s="17" t="s">
+      <c r="D34" s="5">
+        <v>0</v>
+      </c>
+      <c r="E34" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F34" s="5">
@@ -3681,10 +3059,10 @@
         <v>6</v>
       </c>
       <c r="K34" s="5"/>
-      <c r="L34" s="21">
-        <v>1</v>
-      </c>
-      <c r="M34" s="21">
+      <c r="L34" s="18">
+        <v>1</v>
+      </c>
+      <c r="M34" s="18">
         <v>1</v>
       </c>
       <c r="N34" s="5">
@@ -3693,20 +3071,20 @@
       <c r="O34" s="4">
         <v>1</v>
       </c>
-      <c r="P34" s="13">
+      <c r="P34" s="12">
         <v>10</v>
       </c>
       <c r="Q34" s="4">
         <v>1</v>
       </c>
-      <c r="R34" s="13">
+      <c r="R34" s="12">
         <v>1</v>
       </c>
       <c r="S34" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="35" customFormat="1" ht="16.5" spans="1:19">
+    <row r="35" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>105400</v>
       </c>
@@ -3719,13 +3097,13 @@
       <c r="D35" s="4">
         <v>0</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F35" s="4">
         <v>1</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="12" t="s">
         <v>38</v>
       </c>
       <c r="H35" s="3" t="s">
@@ -3738,10 +3116,10 @@
         <v>6</v>
       </c>
       <c r="K35" s="4"/>
-      <c r="L35" s="21">
-        <v>1</v>
-      </c>
-      <c r="M35" s="21">
+      <c r="L35" s="18">
+        <v>1</v>
+      </c>
+      <c r="M35" s="18">
         <v>1</v>
       </c>
       <c r="N35" s="4">
@@ -3750,20 +3128,20 @@
       <c r="O35" s="4">
         <v>1</v>
       </c>
-      <c r="P35" s="13">
+      <c r="P35" s="12">
         <v>20</v>
       </c>
       <c r="Q35" s="4">
         <v>1</v>
       </c>
-      <c r="R35" s="13">
+      <c r="R35" s="12">
         <v>1</v>
       </c>
       <c r="S35" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="36" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="36" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>100800</v>
       </c>
@@ -3773,19 +3151,19 @@
       <c r="C36" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="20">
-        <v>0</v>
-      </c>
-      <c r="E36" s="17" t="s">
+      <c r="D36" s="4">
+        <v>0</v>
+      </c>
+      <c r="E36" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F36" s="4">
         <v>1</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="19" t="s">
         <v>90</v>
       </c>
       <c r="I36" s="4">
@@ -3794,10 +3172,10 @@
       <c r="J36" s="4">
         <v>6</v>
       </c>
-      <c r="L36" s="21">
-        <v>1</v>
-      </c>
-      <c r="M36" s="21">
+      <c r="L36" s="18">
+        <v>1</v>
+      </c>
+      <c r="M36" s="18">
         <v>1</v>
       </c>
       <c r="N36" s="4">
@@ -3806,20 +3184,20 @@
       <c r="O36" s="4">
         <v>1</v>
       </c>
-      <c r="P36" s="13">
+      <c r="P36" s="12">
         <v>20</v>
       </c>
       <c r="Q36" s="4">
         <v>1</v>
       </c>
-      <c r="R36" s="13">
+      <c r="R36" s="12">
         <v>1</v>
       </c>
       <c r="S36" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="37" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="37" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>105300</v>
       </c>
@@ -3829,16 +3207,16 @@
       <c r="C37" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D37" s="20">
-        <v>0</v>
-      </c>
-      <c r="E37" s="17" t="s">
+      <c r="D37" s="4">
+        <v>0</v>
+      </c>
+      <c r="E37" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F37" s="4">
         <v>1</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="12" t="s">
         <v>38</v>
       </c>
       <c r="H37" s="4">
@@ -3850,10 +3228,10 @@
       <c r="J37" s="4">
         <v>5</v>
       </c>
-      <c r="L37" s="21">
-        <v>1</v>
-      </c>
-      <c r="M37" s="21">
+      <c r="L37" s="18">
+        <v>1</v>
+      </c>
+      <c r="M37" s="18">
         <v>1</v>
       </c>
       <c r="N37" s="4">
@@ -3862,20 +3240,20 @@
       <c r="O37" s="4">
         <v>1</v>
       </c>
-      <c r="P37" s="13">
+      <c r="P37" s="12">
         <v>20</v>
       </c>
       <c r="Q37" s="4">
         <v>1</v>
       </c>
-      <c r="R37" s="13">
+      <c r="R37" s="12">
         <v>1</v>
       </c>
       <c r="S37" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="38" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="38" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>105700</v>
       </c>
@@ -3885,16 +3263,16 @@
       <c r="C38" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D38" s="20">
-        <v>0</v>
-      </c>
-      <c r="E38" s="17" t="s">
+      <c r="D38" s="4">
+        <v>0</v>
+      </c>
+      <c r="E38" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F38" s="4">
         <v>1</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="12" t="s">
         <v>38</v>
       </c>
       <c r="H38" s="3" t="s">
@@ -3906,10 +3284,10 @@
       <c r="J38" s="4">
         <v>5</v>
       </c>
-      <c r="L38" s="21">
-        <v>1</v>
-      </c>
-      <c r="M38" s="21">
+      <c r="L38" s="18">
+        <v>1</v>
+      </c>
+      <c r="M38" s="18">
         <v>1</v>
       </c>
       <c r="N38" s="4">
@@ -3918,20 +3296,20 @@
       <c r="O38" s="4">
         <v>1</v>
       </c>
-      <c r="P38" s="13">
+      <c r="P38" s="12">
         <v>20</v>
       </c>
       <c r="Q38" s="4">
         <v>1</v>
       </c>
-      <c r="R38" s="13">
+      <c r="R38" s="12">
         <v>1</v>
       </c>
       <c r="S38" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="39" s="4" customFormat="1" ht="16.5" spans="1:19">
+    <row r="39" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>105800</v>
       </c>
@@ -3941,16 +3319,16 @@
       <c r="C39" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D39" s="20">
-        <v>0</v>
-      </c>
-      <c r="E39" s="17" t="s">
+      <c r="D39" s="4">
+        <v>0</v>
+      </c>
+      <c r="E39" s="15" t="s">
         <v>35</v>
       </c>
       <c r="F39" s="4">
         <v>1</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="12" t="s">
         <v>38</v>
       </c>
       <c r="H39" s="3">
@@ -3962,10 +3340,10 @@
       <c r="J39" s="4">
         <v>7</v>
       </c>
-      <c r="L39" s="21">
-        <v>1</v>
-      </c>
-      <c r="M39" s="21">
+      <c r="L39" s="18">
+        <v>1</v>
+      </c>
+      <c r="M39" s="18">
         <v>1</v>
       </c>
       <c r="N39" s="4">
@@ -3974,20 +3352,20 @@
       <c r="O39" s="4">
         <v>1</v>
       </c>
-      <c r="P39" s="13">
+      <c r="P39" s="12">
         <v>20</v>
       </c>
       <c r="Q39" s="4">
         <v>1</v>
       </c>
-      <c r="R39" s="13">
+      <c r="R39" s="12">
         <v>1</v>
       </c>
       <c r="S39" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="40" customFormat="1" ht="16.5" spans="1:19">
+    <row r="40" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>105500</v>
       </c>
@@ -3997,10 +3375,10 @@
       <c r="C40" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="20">
-        <v>1</v>
-      </c>
-      <c r="E40" s="20" t="s">
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F40" s="4">
@@ -4019,10 +3397,10 @@
         <v>4</v>
       </c>
       <c r="K40" s="4"/>
-      <c r="L40" s="21">
-        <v>1</v>
-      </c>
-      <c r="M40" s="21">
+      <c r="L40" s="18">
+        <v>1</v>
+      </c>
+      <c r="M40" s="18">
         <v>1</v>
       </c>
       <c r="N40" s="4">
@@ -4044,7 +3422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" customFormat="1" ht="16.5" spans="1:19">
+    <row r="41" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>104800</v>
       </c>
@@ -4054,10 +3432,10 @@
       <c r="C41" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="20">
-        <v>0</v>
-      </c>
-      <c r="E41" s="20" t="s">
+      <c r="D41" s="4">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>35</v>
       </c>
       <c r="F41" s="4">
@@ -4076,10 +3454,10 @@
         <v>6</v>
       </c>
       <c r="K41" s="4"/>
-      <c r="L41" s="21">
-        <v>1</v>
-      </c>
-      <c r="M41" s="21">
+      <c r="L41" s="18">
+        <v>1</v>
+      </c>
+      <c r="M41" s="18">
         <v>1</v>
       </c>
       <c r="N41" s="4">
@@ -4101,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" customFormat="1" ht="16.5" spans="1:19">
+    <row r="42" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>105501</v>
       </c>
@@ -4111,10 +3489,10 @@
       <c r="C42" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D42" s="20">
-        <v>1</v>
-      </c>
-      <c r="E42" s="20" t="s">
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F42" s="4">
@@ -4133,10 +3511,10 @@
         <v>4</v>
       </c>
       <c r="K42" s="4"/>
-      <c r="L42" s="21">
-        <v>1</v>
-      </c>
-      <c r="M42" s="21">
+      <c r="L42" s="18">
+        <v>1</v>
+      </c>
+      <c r="M42" s="18">
         <v>1</v>
       </c>
       <c r="N42" s="4">
@@ -4159,8 +3537,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\slot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_9EC3F69143C8EB40125425ADCFDD3C7CB9B2A431" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996BB254-4EE3-409E-A4D5-9DCA2746E4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -342,7 +342,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="100">
   <si>
     <t>游戏ID</t>
   </si>
@@ -639,13 +639,17 @@
   </si>
   <si>
     <t>伽罗宝石1</t>
+  </si>
+  <si>
+    <t>伽罗宝石2</t>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -753,6 +757,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -804,7 +815,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -863,6 +874,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1161,7 +1175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -3536,6 +3550,63 @@
         <v>1</v>
       </c>
     </row>
+    <row r="43" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A43" s="4">
+        <v>105502</v>
+      </c>
+      <c r="B43" s="4">
+        <v>105502001</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F43" s="4">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" s="3">
+        <v>105502101</v>
+      </c>
+      <c r="I43" s="4">
+        <v>3</v>
+      </c>
+      <c r="J43" s="4">
+        <v>4</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="18">
+        <v>1</v>
+      </c>
+      <c r="M43" s="18">
+        <v>1</v>
+      </c>
+      <c r="N43" s="4">
+        <v>5</v>
+      </c>
+      <c r="O43" s="4">
+        <v>1</v>
+      </c>
+      <c r="P43" s="4">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>1</v>
+      </c>
+      <c r="R43" s="4">
+        <v>1</v>
+      </c>
+      <c r="S43" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\slot\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996BB254-4EE3-409E-A4D5-9DCA2746E4D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -33,13 +27,13 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -61,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -85,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="F1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -110,7 +104,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="H1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -145,7 +139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -167,7 +161,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -189,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="L1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -211,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="M1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -243,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="N1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -276,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="P1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -299,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="R1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -324,7 +318,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="S1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -342,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="104">
   <si>
     <t>游戏ID</t>
   </si>
@@ -642,14 +636,31 @@
   </si>
   <si>
     <t>伽罗宝石2</t>
-    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>嗨到底</t>
+  </si>
+  <si>
+    <t>104100101|104100102|104100103|104100104</t>
+  </si>
+  <si>
+    <t>狂野沙滩</t>
+  </si>
+  <si>
+    <t>104200101|104200102|104200103|104200104</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -711,25 +722,156 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -753,19 +895,18 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -784,8 +925,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -808,14 +1135,256 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -876,22 +1445,69 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1169,14 +1785,14 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:S45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
     <col min="2" max="2" width="10.5" style="5" customWidth="1"/>
@@ -1191,7 +1807,7 @@
     <col min="20" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1" ht="21.95" customHeight="1" spans="1:19">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1242,7 +1858,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:19" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A2" s="11" t="s">
         <v>15</v>
       </c>
@@ -1285,7 +1901,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:19" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A3" s="11" t="s">
         <v>18</v>
       </c>
@@ -1328,7 +1944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:19" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" s="1" customFormat="1" ht="16.5" spans="1:19">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1349,7 +1965,7 @@
       <c r="R4" s="12"/>
       <c r="S4" s="14"/>
     </row>
-    <row r="5" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:19">
       <c r="A5" s="11">
         <v>100100</v>
       </c>
@@ -1410,7 +2026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:19">
       <c r="A6" s="11">
         <v>100300</v>
       </c>
@@ -1469,7 +2085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" s="2" customFormat="1" ht="16.5" spans="1:19">
       <c r="A7" s="11">
         <v>100700</v>
       </c>
@@ -1528,7 +2144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="8" s="2" customFormat="1" ht="16.5" spans="1:19">
       <c r="A8" s="11">
         <v>101200</v>
       </c>
@@ -1587,7 +2203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="9" s="2" customFormat="1" ht="16.5" spans="1:19">
       <c r="A9" s="11">
         <v>101400</v>
       </c>
@@ -1646,7 +2262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="10" s="2" customFormat="1" ht="16.5" spans="1:19">
       <c r="A10" s="11">
         <v>102400</v>
       </c>
@@ -1707,7 +2323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="11" s="2" customFormat="1" ht="16.5" spans="1:19">
       <c r="A11" s="11">
         <v>101700</v>
       </c>
@@ -1766,7 +2382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="12" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A12" s="3">
         <v>102200</v>
       </c>
@@ -1824,7 +2440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="13" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A13" s="3">
         <v>102100</v>
       </c>
@@ -1882,7 +2498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="14" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A14" s="3">
         <v>101800</v>
       </c>
@@ -1940,7 +2556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="15" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A15" s="3">
         <v>102500</v>
       </c>
@@ -1998,7 +2614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="16" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A16" s="3">
         <v>102300</v>
       </c>
@@ -2056,7 +2672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="17" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A17" s="3">
         <v>103400</v>
       </c>
@@ -2114,7 +2730,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="18" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A18" s="3">
         <v>103500</v>
       </c>
@@ -2172,7 +2788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="19" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A19" s="3">
         <v>103501</v>
       </c>
@@ -2230,7 +2846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="20" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A20" s="3">
         <v>103600</v>
       </c>
@@ -2288,7 +2904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="21" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A21" s="3">
         <v>102800</v>
       </c>
@@ -2346,7 +2962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="22" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A22" s="3">
         <v>103401</v>
       </c>
@@ -2404,7 +3020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="23" s="3" customFormat="1" ht="16.5" spans="1:19">
       <c r="A23" s="3">
         <v>102000</v>
       </c>
@@ -2462,7 +3078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="24" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A24" s="4">
         <v>103800</v>
       </c>
@@ -2520,7 +3136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="25" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A25" s="4">
         <v>102700</v>
       </c>
@@ -2578,7 +3194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="26" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A26" s="4">
         <v>103700</v>
       </c>
@@ -2636,7 +3252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="27" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A27" s="4">
         <v>103100</v>
       </c>
@@ -2694,7 +3310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="28" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A28" s="4">
         <v>104000</v>
       </c>
@@ -2752,7 +3368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="29" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A29" s="4">
         <v>103900</v>
       </c>
@@ -2810,7 +3426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="30" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A30" s="4">
         <v>101600</v>
       </c>
@@ -2868,7 +3484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="31" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A31" s="4">
         <v>101500</v>
       </c>
@@ -2926,7 +3542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="32" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A32" s="4">
         <v>102600</v>
       </c>
@@ -2984,7 +3600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="33" customFormat="1" ht="16.5" spans="1:19">
       <c r="A33" s="4">
         <v>105000</v>
       </c>
@@ -3041,7 +3657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="34" customFormat="1" ht="16.5" spans="1:19">
       <c r="A34" s="4">
         <v>105100</v>
       </c>
@@ -3098,7 +3714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="35" customFormat="1" ht="16.5" spans="1:19">
       <c r="A35" s="4">
         <v>105400</v>
       </c>
@@ -3155,7 +3771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="36" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A36" s="4">
         <v>100800</v>
       </c>
@@ -3211,7 +3827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="37" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A37" s="4">
         <v>105300</v>
       </c>
@@ -3267,7 +3883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="38" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A38" s="4">
         <v>105700</v>
       </c>
@@ -3323,7 +3939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:19" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="39" s="4" customFormat="1" ht="16.5" spans="1:19">
       <c r="A39" s="4">
         <v>105800</v>
       </c>
@@ -3379,7 +3995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="40" customFormat="1" ht="16.5" spans="1:19">
       <c r="A40" s="4">
         <v>105500</v>
       </c>
@@ -3436,7 +4052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="41" customFormat="1" ht="16.5" spans="1:19">
       <c r="A41" s="4">
         <v>104800</v>
       </c>
@@ -3493,7 +4109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="42" customFormat="1" ht="16.5" spans="1:19">
       <c r="A42" s="4">
         <v>105501</v>
       </c>
@@ -3550,7 +4166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:19" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="43" customFormat="1" ht="16.5" spans="1:19">
       <c r="A43" s="4">
         <v>105502</v>
       </c>
@@ -3607,9 +4223,123 @@
         <v>1</v>
       </c>
     </row>
+    <row r="44" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A44" s="4">
+        <v>104100</v>
+      </c>
+      <c r="B44" s="4">
+        <v>104100001</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="21">
+        <v>0</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F44" s="4">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I44" s="4">
+        <v>3</v>
+      </c>
+      <c r="J44" s="4">
+        <v>5</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="18">
+        <v>1</v>
+      </c>
+      <c r="M44" s="18">
+        <v>1</v>
+      </c>
+      <c r="N44" s="4">
+        <v>20</v>
+      </c>
+      <c r="O44" s="4">
+        <v>1</v>
+      </c>
+      <c r="P44" s="4">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>1</v>
+      </c>
+      <c r="R44" s="4">
+        <v>1</v>
+      </c>
+      <c r="S44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A45" s="4">
+        <v>104200</v>
+      </c>
+      <c r="B45" s="4">
+        <v>104200001</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" s="21">
+        <v>1</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I45" s="4">
+        <v>3</v>
+      </c>
+      <c r="J45" s="4">
+        <v>5</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="18">
+        <v>1</v>
+      </c>
+      <c r="M45" s="18">
+        <v>1</v>
+      </c>
+      <c r="N45" s="4">
+        <v>9</v>
+      </c>
+      <c r="O45" s="4">
+        <v>1</v>
+      </c>
+      <c r="P45" s="4">
+        <v>9</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>1</v>
+      </c>
+      <c r="R45" s="4">
+        <v>1</v>
+      </c>
+      <c r="S45" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -632,10 +632,10 @@
     <t>104800101|104800102|104800103|104800104</t>
   </si>
   <si>
-    <t>伽罗宝石1</t>
-  </si>
-  <si>
     <t>伽罗宝石2</t>
+  </si>
+  <si>
+    <t>伽罗宝石3</t>
   </si>
   <si>
     <t>嗨到底</t>
@@ -660,7 +660,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -714,12 +714,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -881,19 +875,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -902,6 +890,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1253,138 +1247,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1443,9 +1437,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4173,7 +4164,7 @@
       <c r="B43" s="4">
         <v>105502001</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="4" t="s">
         <v>99</v>
       </c>
       <c r="D43" s="4">
@@ -4233,10 +4224,10 @@
       <c r="C44" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D44" s="21">
-        <v>0</v>
-      </c>
-      <c r="E44" s="21" t="s">
+      <c r="D44" s="20">
+        <v>0</v>
+      </c>
+      <c r="E44" s="20" t="s">
         <v>35</v>
       </c>
       <c r="F44" s="4">
@@ -4290,10 +4281,10 @@
       <c r="C45" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D45" s="21">
-        <v>1</v>
-      </c>
-      <c r="E45" s="21" t="s">
+      <c r="D45" s="20">
+        <v>1</v>
+      </c>
+      <c r="E45" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F45" s="4">

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="106">
   <si>
     <t>游戏ID</t>
   </si>
@@ -648,6 +648,12 @@
   </si>
   <si>
     <t>104200101|104200102|104200103|104200104</t>
+  </si>
+  <si>
+    <t>德古拉黑暗财富</t>
+  </si>
+  <si>
+    <t>101900101|101900102|101900103|101900104</t>
   </si>
 </sst>
 </file>
@@ -875,13 +881,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
@@ -1782,7 +1788,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -4328,6 +4334,55 @@
         <v>1</v>
       </c>
     </row>
+    <row r="46" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A46" s="4">
+        <v>101900</v>
+      </c>
+      <c r="B46" s="4">
+        <v>101900001</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="20">
+        <v>0</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F46" s="4">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I46" s="4">
+        <v>6</v>
+      </c>
+      <c r="J46" s="4">
+        <v>6</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="18">
+        <v>1</v>
+      </c>
+      <c r="M46" s="18">
+        <v>1</v>
+      </c>
+      <c r="N46" s="4">
+        <v>20</v>
+      </c>
+      <c r="O46" s="4"/>
+      <c r="P46" s="4"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="BaseInit" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="106">
   <si>
     <t>游戏ID</t>
   </si>
@@ -876,6 +876,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <strike/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -890,18 +902,6 @@
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <strike/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1788,7 +1788,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S46"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -4383,6 +4383,63 @@
         <v>1</v>
       </c>
     </row>
+    <row r="47" customFormat="1" ht="16.5" spans="1:19">
+      <c r="A47" s="4">
+        <v>105200</v>
+      </c>
+      <c r="B47" s="4">
+        <v>105200001</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D47" s="5">
+        <v>0</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F47" s="5">
+        <v>1</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H47" s="5">
+        <v>0</v>
+      </c>
+      <c r="I47" s="5">
+        <v>6</v>
+      </c>
+      <c r="J47" s="5">
+        <v>6</v>
+      </c>
+      <c r="K47" s="5"/>
+      <c r="L47" s="18">
+        <v>1</v>
+      </c>
+      <c r="M47" s="18">
+        <v>1</v>
+      </c>
+      <c r="N47" s="5">
+        <v>10</v>
+      </c>
+      <c r="O47" s="4">
+        <v>1</v>
+      </c>
+      <c r="P47" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>1</v>
+      </c>
+      <c r="R47" s="12">
+        <v>1</v>
+      </c>
+      <c r="S47" s="4">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/slots/resources/sample/BaseInit.xlsx
+++ b/slots/resources/sample/BaseInit.xlsx
@@ -336,7 +336,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="104">
   <si>
     <t>游戏ID</t>
   </si>
@@ -648,12 +648,6 @@
   </si>
   <si>
     <t>104200101|104200102|104200103|104200104</t>
-  </si>
-  <si>
-    <t>德古拉黑暗财富</t>
-  </si>
-  <si>
-    <t>101900101|101900102|101900103|101900104</t>
   </si>
 </sst>
 </file>
@@ -876,19 +870,13 @@
       <charset val="134"/>
     </font>
     <font>
-      <strike/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -900,8 +888,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <strike/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1788,7 +1782,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S47"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="5"/>
@@ -4334,112 +4328,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A46" s="4">
-        <v>101900</v>
-      </c>
-      <c r="B46" s="4">
-        <v>101900001</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" s="20">
-        <v>0</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="F46" s="4">
-        <v>1</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I46" s="4">
-        <v>6</v>
-      </c>
-      <c r="J46" s="4">
-        <v>6</v>
-      </c>
-      <c r="K46" s="4"/>
-      <c r="L46" s="18">
-        <v>1</v>
-      </c>
-      <c r="M46" s="18">
-        <v>1</v>
-      </c>
-      <c r="N46" s="4">
-        <v>20</v>
-      </c>
-      <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-      <c r="Q46" s="4"/>
-      <c r="R46" s="4"/>
-      <c r="S46" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" customFormat="1" ht="16.5" spans="1:19">
-      <c r="A47" s="4">
-        <v>105200</v>
-      </c>
-      <c r="B47" s="4">
-        <v>105200001</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D47" s="5">
-        <v>0</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="F47" s="5">
-        <v>1</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="H47" s="5">
-        <v>0</v>
-      </c>
-      <c r="I47" s="5">
-        <v>6</v>
-      </c>
-      <c r="J47" s="5">
-        <v>6</v>
-      </c>
-      <c r="K47" s="5"/>
-      <c r="L47" s="18">
-        <v>1</v>
-      </c>
-      <c r="M47" s="18">
-        <v>1</v>
-      </c>
-      <c r="N47" s="5">
-        <v>10</v>
-      </c>
-      <c r="O47" s="4">
-        <v>1</v>
-      </c>
-      <c r="P47" s="12">
-        <v>10</v>
-      </c>
-      <c r="Q47" s="4">
-        <v>1</v>
-      </c>
-      <c r="R47" s="12">
-        <v>1</v>
-      </c>
-      <c r="S47" s="4">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
